--- a/trace_compare_final_project/traceability_matrix_export (10) - Copy - Copy_comparison_output.xlsx
+++ b/trace_compare_final_project/traceability_matrix_export (10) - Copy - Copy_comparison_output.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1_old" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison_Output'!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparison_Output'!$A$1:$O$28</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -192,10 +192,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -600,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.59765625" customWidth="1" min="1" max="1"/>
@@ -704,7 +702,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr"/>
-      <c r="C2" s="6" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
@@ -730,23 +728,23 @@
       </c>
       <c r="B3" s="6" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr"/>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Dust/Particulate Control</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
         </is>
@@ -767,52 +765,40 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="57" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000100</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr"/>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr"/>
-      <c r="G4" s="11" t="inlineStr"/>
-      <c r="H4" s="11" t="inlineStr"/>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>Project-SRS-0009</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>Compressed Air Quality</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000101</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Safe, Compliant and Sustainable Operations</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5" ht="42.75" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
@@ -820,220 +806,244 @@
       </c>
       <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="42.75" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Project-BRS-0001</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Safe, Efficient &amp; Compliant Operations</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>The widget factory shall enable safe, efficient, and legally compliant manufacturing operations across all production, logistics, and support activities to protect personnel, assets, and regulatory approvals.</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Project-SRS-0013</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Fire Detection Coverage</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>The facility must provide fire and smoke detection coverage for all occupied and operational spaces.</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Project-BRS-0001</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>Safe, Efficient &amp; Compliant Operations</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>The widget factory shall enable safe, efficient, and legally compliant manufacturing operations across all production, logistics, and support activities to protect personnel, assets, and regulatory approvals.</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Project-SRS-0013</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>Fire Detection Coverage</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>The facility must provide fire and smoke detection coverage for all occupied and operational spaces.</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Workforce Productivity &amp; Support</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Project-SRS-0018</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Physical Security Zones</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O6" s="9" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="7" ht="57" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Project-BRS-0001</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>Safe, Efficient &amp; Compliant Operations</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>The widget factory shall enable safe, efficient, and legally compliant manufacturing operations across all production, logistics, and support activities to protect personnel, assets, and regulatory approvals.</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Project-SRS-0014</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>Fire Suppression</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>The facility must provide fire suppression systems appropriate to the fire hazard classification of each area.</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Project-BRS-0004</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Community Stewardship</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Project-SRS-0017</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Noise at Boundary</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="71.25" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="57" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr"/>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Project-BRS-0001</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Safe, Efficient &amp; Compliant Operations</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>The widget factory shall enable safe, efficient, and legally compliant manufacturing operations across all production, logistics, and support activities to protect personnel, assets, and regulatory approvals.</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Project-SRS-0001</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>Site Access &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Project-SRS-0003</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Floor Load Rating</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
@@ -1043,7 +1053,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>Functional Requirement</t>
+          <t>Technical Requirements</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -1053,219 +1063,147 @@
       </c>
     </row>
     <row r="9" ht="57" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000101</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Reliable Manufacturing Capability</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Project-SRS-0010</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Electrical Power Quality</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42.75" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000101</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Project-SRS-0005</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Building Envelope Tightness</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>Technical Requirements</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0018</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>Physical Security Zones</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="57" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr"/>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0008</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Dust/Particulate Control</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0007</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>Humidity Control</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="71.25" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12" ht="57" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr"/>
       <c r="C12" s="12" t="inlineStr"/>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -1282,59 +1220,59 @@
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0001</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>Site Access &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0018</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Physical Security Zones</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="13" ht="57" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr"/>
       <c r="C13" s="12" t="inlineStr"/>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1351,59 +1289,59 @@
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0006</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>Temperature Control</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0008</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Dust/Particulate Control</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="14" ht="57" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="12" t="inlineStr"/>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1420,59 +1358,59 @@
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Community Stewardship</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0017</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Noise at Boundary</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>Workforce Productivity &amp; Support</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0007</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Humidity Control</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="57" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr"/>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="71.25" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr"/>
       <c r="C15" s="12" t="inlineStr"/>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1491,57 +1429,57 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Project-BRS-0004</t>
+          <t>Project-BRS-0008</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Environmental &amp; Community Stewardship</t>
+          <t>Workforce Productivity &amp; Support</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0016</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>Wastewater Management</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
+          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0001</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Site Access &amp; Logistics</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr"/>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr"/>
       <c r="C16" s="12" t="inlineStr"/>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1558,344 +1496,380 @@
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Project-BRS-0008</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Workforce Productivity &amp; Support</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0006</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Temperature Control</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="57" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr"/>
+      <c r="C17" s="12" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Safe, Compliant and Sustainable Operations</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Environmental &amp; Community Stewardship</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0017</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Noise at Boundary</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="57" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr"/>
+      <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Safe, Compliant and Sustainable Operations</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Project-BRS-0004</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Community Stewardship</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0016</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Wastewater Management</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="57" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr"/>
+      <c r="C19" s="12" t="inlineStr"/>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Project-OBJ-01</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Safe, Compliant and Sustainable Operations</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Project-BRS-0004</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Community Stewardship</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="57" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr"/>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="57" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="12" t="inlineStr"/>
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Project-OBJ-01</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Safe, Compliant and Sustainable Operations</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr"/>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Floor Load Rating</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="57" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr"/>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="57" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr"/>
+      <c r="C21" s="12" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Reliable Manufacturing Capability</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Project-SRS-0010</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>Electrical Power Quality</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="57" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr"/>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr"/>
-      <c r="F19" s="12" t="inlineStr"/>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0008</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>Dust/Particulate Control</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="57" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr"/>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0007</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>Humidity Control</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="71.25" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0002</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>Loading Dock Capacity</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="22" ht="57" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr"/>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="12" t="inlineStr"/>
       <c r="D22" s="12" t="inlineStr"/>
       <c r="E22" s="12" t="inlineStr"/>
@@ -1915,44 +1889,44 @@
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0008</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Dust/Particulate Control</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="23" ht="57" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr"/>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="12" t="inlineStr"/>
       <c r="D23" s="12" t="inlineStr"/>
       <c r="E23" s="12" t="inlineStr"/>
@@ -1972,134 +1946,146 @@
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0009</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>Compressed Air Quality</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="57" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0007</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Humidity Control</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="71.25" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="12" t="inlineStr"/>
       <c r="D24" s="12" t="inlineStr"/>
       <c r="E24" s="12" t="inlineStr"/>
       <c r="F24" s="12" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Project-BRS-0002</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Reliable Manufacturing Capability</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0006</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>Temperature Control</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0002</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Loading Dock Capacity</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
         <is>
           <t>Functional Requirement</t>
         </is>
       </c>
-      <c r="O24" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42.75" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000101</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr"/>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="57" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Project-PS&amp;TR-B-000107</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr"/>
       <c r="C25" s="12" t="inlineStr"/>
       <c r="D25" s="12" t="inlineStr"/>
       <c r="E25" s="12" t="inlineStr"/>
       <c r="F25" s="12" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0005</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>Building Envelope Tightness</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Reliable Manufacturing Capability</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0003</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Floor Load Rating</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O25" s="6" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
@@ -2108,1226 +2094,164 @@
     <row r="26" ht="57" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Project-PS&amp;TR-B-000101</t>
+          <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr"/>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr"/>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>Reliable Manufacturing Capability</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0009</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Compressed Air Quality</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="57" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr"/>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr"/>
-      <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
-      <c r="O27" s="8" t="inlineStr"/>
+      <c r="B27" s="10" t="inlineStr"/>
+      <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="12" t="inlineStr"/>
+      <c r="E27" s="12" t="inlineStr"/>
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Project-BRS-0002</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Reliable Manufacturing Capability</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Project-SRS-0006</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Temperature Control</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>Functional Requirement</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="57" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Project-PS&amp;TR-B-000107</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr"/>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0018</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>Physical Security Zones</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>The facility must implement access control to restrict entry to production and warehouse areas to authorised personnel only.</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="57" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr"/>
-      <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0008</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>Dust/Particulate Control</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="57" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr"/>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0007</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>Humidity Control</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="71.25" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr"/>
-      <c r="C31" s="12" t="inlineStr"/>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0001</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>Site Access &amp; Logistics</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>The facility must provide segregated heavy-vehicle and light-vehicle access routes from the site boundary to designated loading and parking areas.</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="57" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr"/>
-      <c r="C32" s="12" t="inlineStr"/>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>Project-BRS-0008</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>Workforce Productivity &amp; Support</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>The widget factory shall support an efficient, safe, and productive workforce by providing facilities and environments that enable effective operations, maintenance, and supervision.</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0006</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="inlineStr">
-        <is>
-          <t>Temperature Control</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="57" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Community Stewardship</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
-        </is>
-      </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0017</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>Noise at Boundary</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>The facility must limit operational noise at the site boundary to not exceed the specified maximum levels.</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O33" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="57" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr"/>
-      <c r="C34" s="12" t="inlineStr"/>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Community Stewardship</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0016</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="inlineStr">
-        <is>
-          <t>Wastewater Management</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>The facility must treat and/or contain process wastewater to meet the discharge acceptance criteria at the defined discharge point.</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O34" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="57" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr"/>
-      <c r="C35" s="12" t="inlineStr"/>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>Project-BRS-0004</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="inlineStr">
-        <is>
-          <t>Environmental &amp; Community Stewardship</t>
-        </is>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>The widget factory shall operate in a manner that minimises environmental impact and community disturbance, maintaining compliance with environmental obligations and social licence to operate.</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Project-SRS-0004</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Floor Flatness</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>Technical Requirements</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="57" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr"/>
-      <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>Project-OBJ-01</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Safe, Compliant and Sustainable Operations</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>Establish and operate the widget factory as a safe, legally compliant, and environmentally responsible facility that protects personnel, the community, and the organisation’s licence to operate.</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="57" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr"/>
-      <c r="C37" s="12" t="inlineStr"/>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0010</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>Electrical Power Quality</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
-        <is>
-          <t>The facility must provide electrical power to production equipment within the specified voltage variation and harmonic distortion limits.</t>
-        </is>
-      </c>
-      <c r="M37" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="57" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr"/>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="14" t="inlineStr"/>
-      <c r="E38" s="14" t="inlineStr"/>
-      <c r="F38" s="14" t="inlineStr"/>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0008</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>Dust/Particulate Control</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>The facility must limit airborne particulate concentration in designated controlled areas to the specified maximum level.</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="57" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr"/>
-      <c r="C39" s="12" t="inlineStr"/>
-      <c r="D39" s="14" t="inlineStr"/>
-      <c r="E39" s="14" t="inlineStr"/>
-      <c r="F39" s="14" t="inlineStr"/>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0007</t>
-        </is>
-      </c>
-      <c r="K39" s="8" t="inlineStr">
-        <is>
-          <t>Humidity Control</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified relative humidity range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O39" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="71.25" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr"/>
-      <c r="C40" s="12" t="inlineStr"/>
-      <c r="D40" s="14" t="inlineStr"/>
-      <c r="E40" s="14" t="inlineStr"/>
-      <c r="F40" s="14" t="inlineStr"/>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0002</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>Loading Dock Capacity</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>The facility must provide loading docks capable of simultaneously servicing the forecast peak number of heavy vehicles defined in the logistics plan.</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O40" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="57" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr"/>
-      <c r="C41" s="12" t="inlineStr"/>
-      <c r="D41" s="14" t="inlineStr"/>
-      <c r="E41" s="14" t="inlineStr"/>
-      <c r="F41" s="14" t="inlineStr"/>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="57" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr"/>
-      <c r="C42" s="12" t="inlineStr"/>
-      <c r="D42" s="14" t="inlineStr"/>
-      <c r="E42" s="14" t="inlineStr"/>
-      <c r="F42" s="14" t="inlineStr"/>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0009</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>Compressed Air Quality</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>The facility must supply compressed air to production equipment at the specified pressure, flow, and cleanliness class at each point of use.</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="57" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr"/>
-      <c r="C43" s="12" t="inlineStr"/>
-      <c r="D43" s="14" t="inlineStr"/>
-      <c r="E43" s="14" t="inlineStr"/>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>Project-BRS-0002</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>Reliable Manufacturing Capability</t>
-        </is>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>The widget factory shall provide a stable and controlled manufacturing environment capable of supporting continuous, highquality widget production to meet forecast demand and quality objectives.</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0006</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>Temperature Control</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>The facility must maintain production areas within the specified temperature range during operating hours.</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>Functional Requirement</t>
-        </is>
-      </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="42.75" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr"/>
-      <c r="C44" s="12" t="inlineStr"/>
-      <c r="D44" s="14" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0005</t>
-        </is>
-      </c>
-      <c r="K44" s="8" t="inlineStr">
-        <is>
-          <t>Building Envelope Tightness</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t>The building envelope must achieve air leakage performance not exceeding the nominated threshold.</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O44" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="57" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr"/>
-      <c r="C45" s="10" t="inlineStr"/>
-      <c r="D45" s="15" t="inlineStr"/>
-      <c r="E45" s="15" t="inlineStr"/>
-      <c r="F45" s="15" t="inlineStr"/>
-      <c r="G45" s="15" t="inlineStr"/>
-      <c r="H45" s="15" t="inlineStr"/>
-      <c r="I45" s="15" t="inlineStr"/>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>Project-SRS-0003</t>
-        </is>
-      </c>
-      <c r="K45" s="8" t="inlineStr">
-        <is>
-          <t>Floor Load Rating</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>The production floor must support the maximum static and dynamic loads of installed equipment including maintenance lift loads.</t>
-        </is>
-      </c>
-      <c r="M45" s="8" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N45" s="8" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O45" s="8" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="57" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Project-PS&amp;TR-B-000107</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr"/>
-      <c r="C46" s="6" t="inlineStr"/>
-      <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="6" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr"/>
-      <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>Project-SRS-0004</t>
-        </is>
-      </c>
-      <c r="K46" s="9" t="inlineStr">
-        <is>
-          <t>Floor Flatness</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>The production floor must achieve the specified flatness and levelness tolerances required by precision manufacturing equipment.</t>
-        </is>
-      </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="N46" s="9" t="inlineStr">
-        <is>
-          <t>Technical Requirements</t>
-        </is>
-      </c>
-      <c r="O46" s="9" t="inlineStr">
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3481,15 +2405,15 @@
       </c>
     </row>
     <row r="3" ht="57" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
       <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -3591,15 +2515,15 @@
       </c>
     </row>
     <row r="5" ht="57" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0014</t>
@@ -3632,15 +2556,15 @@
       </c>
     </row>
     <row r="6" ht="71.25" customHeight="1">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -3673,12 +2597,12 @@
       </c>
     </row>
     <row r="7" ht="57" customHeight="1">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
@@ -3726,15 +2650,15 @@
       </c>
     </row>
     <row r="8" ht="57" customHeight="1">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -3767,15 +2691,15 @@
       </c>
     </row>
     <row r="9" ht="57" customHeight="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -3808,15 +2732,15 @@
       </c>
     </row>
     <row r="10" ht="71.25" customHeight="1">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -3849,15 +2773,15 @@
       </c>
     </row>
     <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
       <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -3890,12 +2814,12 @@
       </c>
     </row>
     <row r="12" ht="57" customHeight="1">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
@@ -3943,15 +2867,15 @@
       </c>
     </row>
     <row r="13" ht="57" customHeight="1">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
@@ -3984,15 +2908,15 @@
       </c>
     </row>
     <row r="14" ht="57" customHeight="1">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -4025,12 +2949,12 @@
       </c>
     </row>
     <row r="15" ht="57" customHeight="1">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
@@ -4066,9 +2990,9 @@
       </c>
     </row>
     <row r="16" ht="57" customHeight="1">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
       <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
@@ -4119,15 +3043,15 @@
       </c>
     </row>
     <row r="17" ht="57" customHeight="1">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -4160,15 +3084,15 @@
       </c>
     </row>
     <row r="18" ht="57" customHeight="1">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -4201,15 +3125,15 @@
       </c>
     </row>
     <row r="19" ht="71.25" customHeight="1">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
@@ -4242,15 +3166,15 @@
       </c>
     </row>
     <row r="20" ht="57" customHeight="1">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -4283,15 +3207,15 @@
       </c>
     </row>
     <row r="21" ht="57" customHeight="1">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -4324,15 +3248,15 @@
       </c>
     </row>
     <row r="22" ht="57" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -4365,12 +3289,12 @@
       </c>
     </row>
     <row r="23" ht="42.75" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
@@ -4406,15 +3330,15 @@
       </c>
     </row>
     <row r="24" ht="57" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -4647,15 +3571,15 @@
       <c r="O2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="11" t="n"/>
       <c r="J3" s="7" t="n"/>
       <c r="K3" s="6" t="n"/>
       <c r="L3" s="6" t="n"/>
@@ -4697,15 +3621,15 @@
       <c r="O4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
@@ -4714,15 +3638,15 @@
       <c r="O5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
@@ -4731,12 +3655,12 @@
       <c r="O6" s="6" t="n"/>
     </row>
     <row r="7" ht="57" customHeight="1">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
@@ -4784,15 +3708,15 @@
       </c>
     </row>
     <row r="8" ht="57" customHeight="1">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -4825,15 +3749,15 @@
       </c>
     </row>
     <row r="9" ht="57" customHeight="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -4866,15 +3790,15 @@
       </c>
     </row>
     <row r="10" ht="71.25" customHeight="1">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -4907,15 +3831,15 @@
       </c>
     </row>
     <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
       <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -4948,12 +3872,12 @@
       </c>
     </row>
     <row r="12" ht="57" customHeight="1">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
@@ -5001,15 +3925,15 @@
       </c>
     </row>
     <row r="13" ht="57" customHeight="1">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
@@ -5042,15 +3966,15 @@
       </c>
     </row>
     <row r="14" ht="57" customHeight="1">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -5083,12 +4007,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
@@ -5100,9 +4024,9 @@
       <c r="O15" s="6" t="n"/>
     </row>
     <row r="16" ht="57" customHeight="1">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
       <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr"/>
@@ -5153,15 +4077,15 @@
       </c>
     </row>
     <row r="17" ht="57" customHeight="1">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -5194,15 +4118,15 @@
       </c>
     </row>
     <row r="18" ht="57" customHeight="1">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -5235,15 +4159,15 @@
       </c>
     </row>
     <row r="19" ht="71.25" customHeight="1">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
@@ -5276,15 +4200,15 @@
       </c>
     </row>
     <row r="20" ht="57" customHeight="1">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -5317,15 +4241,15 @@
       </c>
     </row>
     <row r="21" ht="57" customHeight="1">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -5358,15 +4282,15 @@
       </c>
     </row>
     <row r="22" ht="57" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -5399,12 +4323,12 @@
       </c>
     </row>
     <row r="23" ht="42.75" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
@@ -5440,15 +4364,15 @@
       </c>
     </row>
     <row r="24" ht="57" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -5514,15 +4438,15 @@
       <c r="O25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n"/>
@@ -5531,15 +4455,15 @@
       <c r="O26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="6" t="n"/>
@@ -5548,12 +4472,12 @@
       <c r="O27" s="6" t="n"/>
     </row>
     <row r="28" ht="57" customHeight="1">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Project-BRS-0008</t>
@@ -5601,15 +4525,15 @@
       </c>
     </row>
     <row r="29" ht="57" customHeight="1">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -5642,15 +4566,15 @@
       </c>
     </row>
     <row r="30" ht="57" customHeight="1">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
       <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -5683,15 +4607,15 @@
       </c>
     </row>
     <row r="31" ht="71.25" customHeight="1">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0001</t>
@@ -5724,15 +4648,15 @@
       </c>
     </row>
     <row r="32" ht="57" customHeight="1">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
       <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -5765,12 +4689,12 @@
       </c>
     </row>
     <row r="33" ht="57" customHeight="1">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Project-BRS-0004</t>
@@ -5818,15 +4742,15 @@
       </c>
     </row>
     <row r="34" ht="57" customHeight="1">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0016</t>
@@ -5859,15 +4783,15 @@
       </c>
     </row>
     <row r="35" ht="57" customHeight="1">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
       <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -5900,12 +4824,12 @@
       </c>
     </row>
     <row r="36" ht="57" customHeight="1">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
       <c r="G36" s="7" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="inlineStr"/>
@@ -5941,9 +4865,9 @@
       </c>
     </row>
     <row r="37" ht="57" customHeight="1">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
       <c r="D37" s="7" t="inlineStr"/>
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr"/>
@@ -5994,15 +4918,15 @@
       </c>
     </row>
     <row r="38" ht="57" customHeight="1">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
       <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0008</t>
@@ -6035,15 +4959,15 @@
       </c>
     </row>
     <row r="39" ht="57" customHeight="1">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="12" t="n"/>
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0007</t>
@@ -6076,15 +5000,15 @@
       </c>
     </row>
     <row r="40" ht="71.25" customHeight="1">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
       <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0002</t>
@@ -6117,15 +5041,15 @@
       </c>
     </row>
     <row r="41" ht="57" customHeight="1">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
       <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
@@ -6158,15 +5082,15 @@
       </c>
     </row>
     <row r="42" ht="57" customHeight="1">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n"/>
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0009</t>
@@ -6199,15 +5123,15 @@
       </c>
     </row>
     <row r="43" ht="57" customHeight="1">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
       <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0006</t>
@@ -6240,12 +5164,12 @@
       </c>
     </row>
     <row r="44" ht="42.75" customHeight="1">
-      <c r="A44" s="12" t="n"/>
-      <c r="B44" s="12" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="6" t="inlineStr"/>
@@ -6281,15 +5205,15 @@
       </c>
     </row>
     <row r="45" ht="57" customHeight="1">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
       <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Project-SRS-0003</t>
